--- a/AI Planning/Job Scheduling/Job To Machine/problemset/solution/sjf/delivery-10j-3m-1_10tr-uniformd-8c_sjf.xlsx
+++ b/AI Planning/Job Scheduling/Job To Machine/problemset/solution/sjf/delivery-10j-3m-1_10tr-uniformd-8c_sjf.xlsx
@@ -458,187 +458,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Avenida carrera 41 # 35-89 Sur 278441 Bagadó, Chocó</t>
+          <t>Diagonal 22 # 3-67 Sur 731165 Dolores, Tolima</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Andrés</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Transversal 1ª # 34-7 Torre 3 apartamento 7 503693 Puerto Concordia, Meta</t>
+          <t>Transversal 1 Este # 81-98 Este Apartamento 3 271247 El Cantón del San Pablo, Chocó</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Andrés</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cr. 75 # 7-59 Este 473667 Tenerife, Magdalena</t>
+          <t>Tr. 195N # 1-39 Este 543396 Villa Caro, Norte de Santander</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brayan</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cr. 8K # 40M-47 Este Local 8 050909 Buriticá, Antioquia</t>
+          <t>Calle 93O # 6-23 523742 La Tola, Nariño</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brayan</t>
+          <t>Alejandro</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Calle 74 # 95-6 Bodega 777 252532 Granada, Cundinamarca</t>
+          <t>Carrera 28 # 11-73 Sur 201532 Gamarra, Cesar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brayan</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Calle 56 # 2-6 Sur Torre 4 apartamento 137 134780 Altos del Rosario, Bolívar</t>
+          <t>Carrera 132 Bis U # 3-56 Sur Apartamento 88 683527 San Joaquín, Santander</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brayan</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
         <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tr. 79 # 5-66 Sur 056818 Abejorral, Antioquia</t>
+          <t>Cr. 54 # 21-76 Apto. 65 500190 Fuente de Oro, Meta</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brayan</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Carrera 51 # 10-85 Sur Etapa 5 apartamento 72 086327 Santa Lucía, Atlántico</t>
+          <t>Avenida calle 33 # 86-5 Sur 172807 Filadelfia, Caldas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jesús</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Av. Moreno # 6-65 Sur 862879 Orito, Putumayo</t>
+          <t>Carrera 58 # 2-5 Sur Local 76 150278 Sutatenza, Boyacá</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jesús</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>8</v>
